--- a/backtest_runs/20260410_193731/by_symbol/SNGP/SNGP.xlsx
+++ b/backtest_runs/20260410_193731/by_symbol/SNGP/SNGP.xlsx
@@ -465,12 +465,12 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>same_side_as_oracle</t>
+          <t>same_side_as_actual</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>daily_pnl_diff_oracle_minus_model</t>
+          <t>daily_pnl_diff_actual_minus_model</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
@@ -480,7 +480,7 @@
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>suggestion_oracle</t>
+          <t>suggestion_actual</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
@@ -490,7 +490,7 @@
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>daily_pnl_oracle</t>
+          <t>daily_pnl_actual</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
@@ -500,7 +500,7 @@
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>equity_oracle</t>
+          <t>equity_actual</t>
         </is>
       </c>
     </row>
@@ -630,10 +630,10 @@
         </is>
       </c>
       <c r="I4" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K4" s="2" t="n">
         <v>110365.56</v>
@@ -676,10 +676,10 @@
         </is>
       </c>
       <c r="I5" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J5" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K5" s="2" t="n">
         <v>110365.56</v>
@@ -771,7 +771,7 @@
         <v>-2997.139999999996</v>
       </c>
       <c r="J7" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K7" s="3" t="n">
         <v>107368.42</v>
@@ -817,7 +817,7 @@
         <v>-519.3600000000043</v>
       </c>
       <c r="J8" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K8" s="3" t="n">
         <v>106849.06</v>
@@ -863,7 +863,7 @@
         <v>-486.900000000003</v>
       </c>
       <c r="J9" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K9" s="3" t="n">
         <v>106362.16</v>
@@ -906,10 +906,10 @@
         </is>
       </c>
       <c r="I10" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K10" s="2" t="n">
         <v>106362.16</v>
@@ -1044,10 +1044,10 @@
         </is>
       </c>
       <c r="I13" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J13" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K13" s="2" t="n">
         <v>110030.14</v>
@@ -1093,7 +1093,7 @@
         <v>-1839.400000000003</v>
       </c>
       <c r="J14" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K14" s="3" t="n">
         <v>108190.74</v>
@@ -1185,7 +1185,7 @@
         <v>-4165.700000000009</v>
       </c>
       <c r="J16" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K16" s="3" t="n">
         <v>107812.04</v>
@@ -1231,7 +1231,7 @@
         <v>-313.7799999999914</v>
       </c>
       <c r="J17" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K17" s="3" t="n">
         <v>107498.26</v>
@@ -1277,7 +1277,7 @@
         <v>-887.240000000008</v>
       </c>
       <c r="J18" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K18" s="3" t="n">
         <v>106611.02</v>
@@ -1323,7 +1323,7 @@
         <v>-681.6599999999951</v>
       </c>
       <c r="J19" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K19" s="3" t="n">
         <v>105929.36</v>
@@ -1415,7 +1415,7 @@
         <v>-3278.460000000001</v>
       </c>
       <c r="J21" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K21" s="3" t="n">
         <v>106091.66</v>
@@ -1461,7 +1461,7 @@
         <v>-638.3800000000037</v>
       </c>
       <c r="J22" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K22" s="3" t="n">
         <v>105453.28</v>
@@ -1553,7 +1553,7 @@
         <v>-151.4800000000006</v>
       </c>
       <c r="J24" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K24" s="3" t="n">
         <v>105831.98</v>
